--- a/nirmaan_stack/services/boq_parser/tests/fixtures/synthetic_pattern_2_rate.xlsx
+++ b/nirmaan_stack/services/boq_parser/tests/fixtures/synthetic_pattern_2_rate.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,10 +429,15 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>PHASE-1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>PHASE-2</t>
         </is>
@@ -451,30 +456,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -489,22 +499,27 @@
           <t>Electrical works</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>10</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1000</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>20</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>110</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2200</v>
       </c>
     </row>
@@ -517,29 +532,34 @@
           <t>Civil works</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>200</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>1000</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>8</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>200</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1600</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
